--- a/data/datasets/xhs_2026-02-07_studyabroad/processed/comments_cleaned.xlsx
+++ b/data/datasets/xhs_2026-02-07_studyabroad/processed/comments_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,11 +447,6 @@
           <t>likes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -464,26 +459,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>评论区说过的我就不重复了。我说一个鲜少有人提到的：国外生活可以让你在剥离了原生家庭的所有好坏条件之后重新回到你自己身上看看自己到底是谁、以及自己到底能在这个世界上如何立足</t>
+          <t>I won’t repeat what’s already been said in the comments. I’ll mention something rarely brought up: living abroad lets you strip away all the good and bad conditions of your original family and come back to yourself to see who you really are and how you can stand on your own in this world.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>昨天21:14</t>
+          <t>Yesterday 21:14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>4342</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1,游99,评论区说过的我就不重复了。我说一个鲜少有人提到的：国外生活可以让你在剥离了原生家庭的所有好坏条件之后重新回到你自己身上看看自己到底是谁、以及自己到底能在这个世界上如何立足,昨天21:14,中国香港,4342</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -497,26 +487,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>太对了！！！完全脱离原生环境和噪音才能真正意识到自己到底想要成为什么样的人</t>
+          <t>So true!!! Only by completely breaking away from your original environment and noise can you truly realize what kind of person you want to become.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>昨天23:48</t>
+          <t>Yesterday 23:48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>Hubei</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1102</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2,今天早睡了吗,太对了！！！完全脱离原生环境和噪音才能真正意识到自己到底想要成为什么样的人,昨天23:48,湖北,1102</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -530,26 +515,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>作为明显的少数群体生活在国外才能体会到尊重多样性的必要不认为有哪个文明就是比别的文明优越的</t>
+          <t>As a clear minority group living abroad, you come to understand the necessity of respecting diversity and don’t believe any civilization is superior to others.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>昨天01:31</t>
+          <t>Yesterday 01:31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>Sichuan</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3673</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3,巴一刀,作为明显的少数群体生活在国外才能体会到尊重多样性的必要不认为有哪个文明就是比别的文明优越的,昨天01:31,四川,3673</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -563,26 +543,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trueeee！</t>
+          <t>Trueeee!</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>昨天12:03</t>
+          <t>Yesterday 12:03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>168</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4,奇异果大侠,Trueeee！,昨天12:03,美国,168</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -596,26 +571,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>我觉得最大的价值是怎么着都能活着</t>
+          <t>I think the biggest value is just being able to survive no matter what.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>昨天14:26</t>
+          <t>Yesterday 14:26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1097</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>5,糖糖教教主糖小包,我觉得最大的价值是怎么着都能活着,昨天14:26,澳大利亚,1097</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -629,26 +599,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>中产留学心得精华总结</t>
+          <t>A perfect summary of middle-class study abroad insights.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>昨天23:38</t>
+          <t>Yesterday 23:38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>Heilongjiang</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>229</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6,123456789123456789123456,中产留学心得精华总结,昨天23:38,黑龙江,229</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -662,26 +627,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>尽早懂得no one is coming</t>
+          <t>Learn early that no one is coming.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>昨天18:10</t>
+          <t>Yesterday 18:10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1275</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7,气球小猪TiTi,尽早懂得no one is coming,昨天18:10,广东,1275</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -695,26 +655,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>点了想找依靠的时候就想不要输给这个瞬间</t>
+          <t>Clicked because when you want to find support, you think, don’t lose to this moment.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>昨天19:46</t>
+          <t>Yesterday 19:46</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>301</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>8,小太阳,点了想找依靠的时候就想不要输给这个瞬间,昨天19:46,中国香港,301</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -728,26 +683,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>还有一点很重要会做饭了哈哈哈出国几年回来发现大部分朋友还是不太会做饭</t>
+          <t>Another important thing: learning to cook haha. After being abroad for years and coming back, I found most friends still can’t really cook.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8分钟前</t>
+          <t>8 minutes ago</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>9,一二三,还有一点很重要会做饭了哈哈哈出国几年回来发现大部分朋友还是不太会做饭,8分钟前,中国香港,0</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -761,26 +711,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>国外感觉是一种评价体系中的真空你暂时脱离了国内的评价体系但你也还没有进入他们的评价体系里面</t>
+          <t>Abroad feels like a vacuum in the evaluation system—you temporarily leave the domestic system but haven’t yet entered theirs.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>昨天14:20</t>
+          <t>Yesterday 14:20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>651</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10,灰化百香果,国外感觉是一种评价体系中的真空你暂时脱离了国内的评价体系但你也还没有进入他们的评价体系里面,昨天14:20,英国,651</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -794,26 +739,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>非常到位的评价感觉留学过程中在建立自我的评价标准</t>
+          <t>Such an accurate comment, it feels like you’re building your own standards of evaluation during studying abroad.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15小时前</t>
+          <t>15 hours ago</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>86</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>11,薄荷吉利丁,非常到位的评价感觉留学过程中在建立自我的评价标准,15小时前,加拿大,86</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -827,26 +767,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>我说个别的吧我是出国上学之后才意识到生病是可以在家休息的</t>
+          <t>Here’s something else: I only realized after going abroad for school that you can actually rest at home when you’re sick.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9分钟前</t>
+          <t>9 minutes ago</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>12,你走了我们吃什么,我说个别的吧我是出国上学之后才意识到生病是可以在家休息的,9分钟前,广东,2</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -860,26 +795,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>我一个人能干所有事情没有事情可以难到我不再惧怕一个人</t>
+          <t>I can do everything on my own, nothing can scare me anymore about being alone.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11小时前</t>
+          <t>11 hours ago</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>5</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>13,今天喝茶了吗,我一个人能干所有事情没有事情可以难到我不再惧怕一个人,11小时前,中国香港,5</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -893,26 +823,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>留学带给个人独立生存的能力自我学习自我管理的能力世界性的眼界和批判性思维</t>
+          <t>Studying abroad brings the ability to live independently, self-learning, self-management, a global perspective, and critical thinking.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34分钟前</t>
+          <t>34 minutes ago</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>Shandong</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>14,理性多一点,留学带给个人独立生存的能力自我学习自我管理的能力世界性的眼界和批判性思维,34分钟前,山东,1</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -926,26 +851,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>开始学会识别自我将真正的自我与他人剥离解绑精神自由</t>
+          <t>You start learning to recognize yourself, separating your true self from others, achieving spiritual freedom.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>昨天09:29</t>
+          <t>Yesterday 09:29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>418</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>15,momo,开始学会识别自我将真正的自我与他人剥离解绑精神自由,昨天09:29,加拿大,418</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -959,26 +879,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>会更加包容</t>
+          <t>You become more tolerant.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32分钟前</t>
+          <t>32 minutes ago</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>Hebei</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>16,小红薕65BAD31B,会更加包容,32分钟前,河北,1</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -992,26 +907,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>唯一的能力可能就是现在把我发配到任何一个国家我也能想办法稳住心态活下来</t>
+          <t>My only skill now might be that I can be sent to any country and still find a way to keep my cool and survive.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>昨天21:37</t>
+          <t>Yesterday 21:37</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>Shandong</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>182</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>17,啊吧啊吧,唯一的能力可能就是现在把我发配到任何一个国家我也能想办法稳住心态活下来,昨天21:37,山东,182</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1025,26 +935,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>这是真的对恶劣的环境手拿把搴</t>
+          <t>This is real—like holding a weapon against harsh environments.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>18,烂花剩手,这是真的对恶劣的环境手拿把搴,20小时前,格鲁吉亚,17</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -1058,26 +963,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>独立思考的能力剥离固有视角看待问题以自我为中心的思考找到内驱力等等</t>
+          <t>The ability to think independently, strip away ingrained perspectives, view problems without self-centeredness, find inner motivation, and so on.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>昨天19:05</t>
+          <t>Yesterday 19:05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>433</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>19,momo,独立思考的能力剥离固有视角看待问题以自我为中心的思考找到内驱力等等,昨天19:05,上海,433</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -1091,26 +991,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>哦哦还有最重要的尊重和平等尊重他人生活没有人谁比谁更高贵</t>
+          <t>Oh, and the most important: respect and equality, respecting others’ lives—no one is nobler than anyone else.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>昨天19:07</t>
+          <t>Yesterday 19:07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>167</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>20,momo,哦哦还有最重要的尊重和平等尊重他人生活没有人谁比谁更高贵,昨天19:07,上海,167</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1124,26 +1019,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>看世界的视角完全变了在国外完全是更加自由更加宏观地看问题没有了网络和言论的很大限制</t>
+          <t>My perspective on the world has completely changed. Being abroad feels way freer and more broad-minded when looking at issues, without the heavy restrictions on the internet and speech.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8小时前</t>
+          <t>8 hours ago</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>20</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>21,ALUER~,看世界的视角完全变了在国外完全是更加自由更加宏观地看问题没有了网络和言论的很大限制,8小时前,德国,20</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -1157,26 +1047,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>我觉得最重要的是跳出塑造你形成你认知的窠臼留学逼迫你在两个文明两个语言两个社会的间隙中挣扎碰撞</t>
+          <t>I think the most important thing is breaking out of the mold that shapes your cognition. Studying abroad forces you to struggle and clash between two civilizations, two languages, and two societies.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>Shanxi</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>226</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>22,X大侠,我觉得最重要的是跳出塑造你形成你认知的窠臼留学逼迫你在两个文明两个语言两个社会的间隙中挣扎碰撞,1天前,山西,226</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -1190,26 +1075,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>是的能不能得到取决于自身的认知理解和接纳度</t>
+          <t>Yes, whether you gain something depends on your own understanding, acceptance, and cognition.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>昨天14:00</t>
+          <t>Yesterday 14:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>13</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>23,兔纸,是的能不能得到取决于自身的认知理解和接纳度,昨天14:00,加拿大,13</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1223,26 +1103,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>我回来之后变得别人给我东西我欣然接受好呀谢谢然后被我妈一记差点头都打掉</t>
+          <t>After I came back, I happily accepted whatever people gave me, saying 'Great, thanks!' Then my mom almost knocked my head off for it.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>2 hours ago</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>Jiangsu</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>24,吃了会瘦的白芝豆,我回来之后变得别人给我东西我欣然接受好呀谢谢然后被我妈一记差点头都打掉,2小时前,江苏,1</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -1256,26 +1131,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>低语境文化和高语境文化区别</t>
+          <t>The difference between low-context and high-context cultures.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>25,Sally,低语境文化和高语境文化区别,1小时前,澳大利亚,0</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -1289,26 +1159,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>学会和自己独处</t>
+          <t>Learning to be alone with yourself.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>昨天11:47</t>
+          <t>Yesterday 11:47</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>461</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>26,À la prochaine,学会和自己独处,昨天11:47,法国,461</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -1322,26 +1187,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>完全陌生的国家和社会文化是内心感受的放大器</t>
+          <t>A completely unfamiliar country and social culture acts like an amplifier for your inner feelings.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>昨天11:49</t>
+          <t>Yesterday 11:49</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>282</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>27,À la prochaine,完全陌生的国家和社会文化是内心感受的放大器,昨天11:49,法国,282</t>
-        </is>
       </c>
     </row>
     <row r="29">
@@ -1355,26 +1215,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>人不是必需往高处走也可以往四处走</t>
+          <t>People don’t have to always move upwards; they can also move in all directions.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>昨天20:37</t>
+          <t>Yesterday 20:37</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>168</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>28,Mr.陳,人不是必需往高处走也可以往四处走,昨天20:37,上海,168</t>
-        </is>
       </c>
     </row>
     <row r="30">
@@ -1388,26 +1243,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>说得好好</t>
+          <t>Well said.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>昨天21:30</t>
+          <t>Yesterday 21:30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>29,建材李哥668,说得好好,昨天21:30,北京,1</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -1421,26 +1271,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>支持那个怎么样都能活着然后回国真的觉得生活中全是没注意过的美好</t>
+          <t>Support for the idea that no matter what, you can survive. Then coming back home really makes you feel life is full of unnoticed beauty.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>2 hours ago</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>6</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>30,z52527,支持那个怎么样都能活着然后回国真的觉得生活中全是没注意过的美好,2小时前,北京,6</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -1454,26 +1299,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>好厉害</t>
+          <t>So impressive.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>2 hours ago</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>Fujian</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>31,小红薕6793AE23,好厉害,2小时前,福建,0</t>
-        </is>
       </c>
     </row>
     <row r="33">
@@ -1487,26 +1327,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>看到小红书还有人在问这样的问题而不是不管不顾给留学生群体贴标签真是太感动了</t>
+          <t>Seeing people on Xiaohongshu still asking these kinds of questions instead of blindly labeling international students is really touching.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>昨天17:12</t>
+          <t>Yesterday 17:12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>264</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>32,野原,看到小红书还有人在问这样的问题而不是不管不顾给留学生群体贴标签真是太感动了,昨天17:12,美国,264</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -1520,26 +1355,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>是的我和妊有同样的感受</t>
+          <t>Yes, I share the same feelings as Ren.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>13 hours ago</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>33,云吃吃的阅食行记,是的我和妊有同样的感受,13小时前,上海,1</t>
-        </is>
       </c>
     </row>
     <row r="35">
@@ -1553,26 +1383,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>没留过学的真诚发问那些说怎么样都能活的国内背井离乡的打工人不也是这样吗</t>
+          <t>A sincere question from someone who hasn’t studied abroad: aren’t those domestic migrant workers who say 'no matter what, you can survive' basically the same?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>Shanxi</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>34,枕月眠,没留过学的真诚发问那些说怎么样都能活的国内背井离乡的打工人不也是这样吗,1小时前,山西,0</t>
-        </is>
       </c>
     </row>
     <row r="36">
@@ -1586,26 +1411,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>因为在中国再背井离乡你也还是在同一文化圈和语言区很难触发对不同文化的思考</t>
+          <t>Because even if you leave your hometown in China, you’re still in the same cultural and language circle, so it’s hard to trigger thinking about different cultures.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>5</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>35,Sally,因为在中国再背井离乡你也还是在同一文化圈和语言区很难触发对不同文化的思考,1小时前,澳大利亚,5</t>
-        </is>
       </c>
     </row>
     <row r="37">
@@ -1619,26 +1439,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>就是对名校祢魅了包括清北感觉大家都差不多</t>
+          <t>It’s like being obsessed with prestigious schools, including Tsinghua and Peking University, it feels like everyone is pretty much the same.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>昨天18:48</t>
+          <t>Yesterday 18:48</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>Henan</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>110</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>36,小比熊蹦蹦,就是对名校祢魅了包括清北感觉大家都差不多,昨天18:48,河南,110</t>
-        </is>
       </c>
     </row>
     <row r="38">
@@ -1652,26 +1467,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>这一点好像没有人说我觉得是在国外有一个非常尊重且开放的环境让你可以作为一个独立的个体</t>
+          <t>No one seems to mention this, but I think abroad there’s a very respectful and open environment that lets you be an independent individual.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>昨天10:41</t>
+          <t>Yesterday 10:41</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>119</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>37,momo,这一点好像没有人说我觉得是在国外有一个非常尊重且开放的环境让你可以作为一个独立的个体,昨天10:41,加拿大,119</t>
-        </is>
       </c>
     </row>
     <row r="39">
@@ -1685,26 +1495,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>我是海本海硕个人感觉没有什么知识是必须亲身留学才能获得的</t>
+          <t>I did my undergrad and master’s abroad, and personally I feel there’s no knowledge you absolutely must get by studying abroad.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>2 days ago</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>55</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>38,葡萄啵啵茶,我是海本海硕个人感觉没有什么知识是必须亲身留学才能获得的,2天前,上海,55</t>
-        </is>
       </c>
     </row>
     <row r="40">
@@ -1718,26 +1523,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>知识能怎么不同肯定大差不差呀其他方面你海本海硕没有对比当然看不出差别</t>
+          <t>How different can knowledge really be? It’s definitely not that different. In other aspects, if you haven’t compared undergrad and master’s abroad, of course you won’t see the difference.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>2 days ago</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>128</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>39,米米,知识能怎么不同肯定大差不差呀其他方面你海本海硕没有对比当然看不出差别,2天前,美国,128</t>
-        </is>
       </c>
     </row>
     <row r="41">
@@ -1751,26 +1551,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>刚留学去口语 workshop的时候主持的学校工作人员是个一米八染紫色头发烟熔妆加各种环的女士</t>
+          <t>When I first went to a speaking workshop abroad, the host was a school staff member about 1.8m tall with purple dyed hair, smokey makeup, and all kinds of piercings.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>13 hours ago</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>20</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>40,小红薕65c82a8000000001f018cb7,刚留学去口语 workshop的时候主持的学校工作人员是个一米八染紫色头发烟熔妆加各种环的女士,13小时前,美国,20</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -1784,26 +1579,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>在国内的时候看到大花臂都躲着走平时也没有接触的机会但是出国之后同班同学就是大花臂</t>
+          <t>Back home, I used to avoid people with big floral tattoos and never had the chance to interact with them, but after going abroad, my classmates all have big floral tattoos.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12小时前</t>
+          <t>12 hours ago</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>15</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>41,Eva学姐_Data留学,在国内的时候看到大花臂都躲着走平时也没有接触的机会但是出国之后同班同学就是大花臂,12小时前,美国,15</t>
-        </is>
       </c>
     </row>
     <row r="43">
@@ -1817,26 +1607,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>我不是留子但是十年前有幸跟着两个留子好友去过两个国家旅行过两个多月</t>
+          <t>I'm not an overseas student, but ten years ago I was lucky enough to travel for over two months with two overseas student friends to two countries.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4小时前</t>
+          <t>4 hours ago</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>4</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>42,星稀,我不是留子但是十年前有幸跟着两个留子好友去过两个国家旅行过两个多月,4小时前,广东,4</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -1850,26 +1635,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>最后一句话是什么意思</t>
+          <t>What does the last sentence mean?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>Anhui</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>43,CJR088,最后一句话是什么意思,1小时前,安徽,0</t>
-        </is>
       </c>
     </row>
     <row r="45">
@@ -1883,26 +1663,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>我只学会了一样东西叫活在当下虽然也会对学业工作焦虑但是我不会习惯性地花很长时间沉浸在痛苦之中</t>
+          <t>The only thing I've learned is to live in the moment. Although I do get anxious about school and work, I don't habitually spend a long time drowning in pain.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>昨天14:36</t>
+          <t>Yesterday 14:36</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>86</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>44,Bebé del melocotón,我只学会了一样东西叫活在当下虽然也会对学业工作焦虑但是我不会习惯性地花很长时间沉浸在痛苦之中,昨天14:36,西班牙,86</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -1916,26 +1691,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>更早一点让你知道自己比较适合过哪一种生活</t>
+          <t>The earlier you know, the better you understand which kind of life suits you.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>昨天22:58</t>
+          <t>Yesterday 22:58</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>12</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>45,Lily,更早一点让你知道自己比较适合过哪一种生活,昨天22:58,广东,12</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -1949,26 +1719,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>确实</t>
+          <t>Exactly.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15小时前</t>
+          <t>15 hours ago</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>Tianjin</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>46,Offer蛙必有offer,确实,15小时前,天津,0</t>
-        </is>
       </c>
     </row>
     <row r="48">
@@ -1982,26 +1747,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>很自由但这种自由不来自于西方文化的freedom而来源于你作为外国暂居者的身份</t>
+          <t>It's very free, but this kind of freedom doesn't come from Western culture's idea of freedom; it comes from your identity as a foreigner temporarily living abroad.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>Zhejiang</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>5</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>47,桥岸泥,很自由但这种自由不来自于西方文化的freedom而来源于你作为外国暂居者的身份,1小时前,浙江,5</t>
-        </is>
       </c>
     </row>
     <row r="49">
@@ -2015,26 +1775,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>我懂这个</t>
+          <t>I get this.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>Liaoning</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>48,IVYVI,我懂这个,1小时前,辽宁,1</t>
-        </is>
       </c>
     </row>
     <row r="50">
@@ -2048,26 +1803,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>对任何人祢魅也对任何人尊重多了同理心有些人和事可能自身不理解但尊重存在的权利</t>
+          <t>More charm and respect towards everyone, more empathy. Some people and things you might not understand yourself, but you respect their right to exist.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4小时前</t>
+          <t>4 hours ago</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>卡塔尔</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>8</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>49,沫光微浅,对任何人祢魅也对任何人尊重多了同理心有些人和事可能自身不理解但尊重存在的权利,4小时前,卡塔尔,8</t>
-        </is>
       </c>
     </row>
     <row r="51">
@@ -2081,26 +1831,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>批判性思维 critical thinking</t>
+          <t>Critical thinking.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7小时前</t>
+          <t>7 hours ago</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>Jiangsu</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>3</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>50,灯喵喵,批判性思维 critical thinking,7小时前,江苏,3</t>
-        </is>
       </c>
     </row>
     <row r="52">
@@ -2114,26 +1859,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>批判性思维 critical thinking</t>
+          <t>Critical thinking.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7小时前</t>
+          <t>7 hours ago</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>Jiangsu</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>3</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>51,灯塔咩咩,批判性思维 critical thinking,7小时前,江苏,3</t>
-        </is>
       </c>
     </row>
     <row r="53">
@@ -2147,26 +1887,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>中国人在国外很抱团，在国内就是一盘散沙</t>
+          <t>Chinese people stick together abroad, but back home, we're just scattered like loose sand.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5小时前</t>
+          <t>5 hours ago</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>Shandong</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>6</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>52,SummerToToTo,中国人在国外很抱团，在国内就是一盘散沙,5小时前,山东,6</t>
-        </is>
       </c>
     </row>
     <row r="54">
@@ -2180,26 +1915,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>哪儿重要？肉身重要。（我还没有走出去的勇气</t>
+          <t>What's important? The physical self is important. (I still don't have the courage to step out yet.)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>71</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>53,布朗熊,哪儿重要？肉身重要。（我还没有走出去的勇气,20小时前,澳大利亚,71</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -2213,26 +1943,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>开阔眼界以及独立生活能力，其余的应该跟出国留学没什么关关系哈</t>
+          <t>Broadening horizons and independent living skills; the rest probably has nothing to do with studying abroad.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11小时前</t>
+          <t>11 hours ago</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>2</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>54,吉良吉影想过平静的生活,开阔眼界以及独立生活能力，其余的应该跟出国留学没什么关关系哈,11小时前,澳大利亚,2</t>
-        </is>
       </c>
     </row>
     <row r="56">
@@ -2246,26 +1971,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>如何判断一件事情呢？大陆很多学校，在思想上就是禁止你思考这部分的。在台湾，因为还有一点政治自由…所以可以。我已经不止一次在两地遇到很多大陆的人跟我说：你的想法…很危险</t>
+          <t>How to judge something? Many schools in mainland China forbid you from thinking about certain things. In Taiwan, because there's a bit of political freedom... it's possible. I've met many mainland people in both places who told me: Your ideas... are very dangerous.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>中国台湾</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>6</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>55,7777733338,如何判断一件事情呢？大陆很多学校，在思想上就是禁止你思考这部分的。在台湾，因为还有一点政治自由…所以可以。我已经不止一次在两地遇到很多大陆的人跟我说：你的想法…很危险,1小时前,中国台湾,6</t>
-        </is>
       </c>
     </row>
     <row r="57">
@@ -2279,26 +1999,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>因为不同的环国和文化是给人带来体验，学会接受和尊重不同，不是去把别人变成自己</t>
+          <t>Because different countries and cultures bring experiences, you learn to accept and respect differences, not to turn others into yourself.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>13 hours ago</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>3</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>56,小葱阿姨爱做饭,因为不同的环国和文化是给人带来体验，学会接受和尊重不同，不是去把别人变成自己,13小时前,美国,3</t>
-        </is>
       </c>
     </row>
     <row r="58">
@@ -2312,26 +2027,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>体会到虽然每个地方都是屎山，但屎山都不一样</t>
+          <t>Realizing that although every place is a pile of shit, every pile of shit is different.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>2 hours ago</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>29</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>57,米娅的小院儿,体会到虽然每个地方都是屎山，但屎山都不一样,2小时前,德国,29</t>
-        </is>
       </c>
     </row>
     <row r="59">
@@ -2345,26 +2055,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>认知上带来的最大改变莫过于发现没有什么事情是理所应当的，进而停止索取，学会感恩</t>
+          <t>The biggest change in cognition is realizing that nothing is owed to you, which leads to stopping demands and learning gratitude.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>2 hours ago</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>12</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>58,星野_,认知上带来的最大改变莫过于发现没有什么事情是理所应当的，进而停止索取，学会感恩,2小时前,美国,12</t>
-        </is>
       </c>
     </row>
     <row r="60">
@@ -2378,26 +2083,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>当然是眼界的开拓，看待文化与学科的更多元化思维，以及当地大佬的学术资源</t>
+          <t>Of course, it's about broadening horizons, having more diverse ways of thinking about culture and disciplines, and accessing the academic resources of local big shots.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16小时前</t>
+          <t>16 hours ago</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>59,Leona不吃草,当然是眼界的开拓，看待文化与学科的更多元化思维，以及当地大佬的学术资源,16小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="61">
@@ -2411,26 +2111,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>选修了门gender sexuality feminism的课程</t>
+          <t>I took an elective course on gender, sexuality, and feminism.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>4</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>60,皮皮熊猫,选修了门gender sexuality feminism的课程,1天前,英国,4</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -2444,26 +2139,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>开拓眼界吧，在留学期间会去很多国家旅游，接触到不同的文化，会更加尊重包容不同</t>
+          <t>Broaden your horizons. During studying abroad, you'll travel to many countries, experience different cultures, and learn to respect and embrace diversity.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>61,Minisue苏苏子,开拓眼界吧，在留学期间会去很多国家旅游，接触到不同的文化，会更加尊重包容不同,1小时前,德国,1</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -2477,26 +2167,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>出国最大的收获就是了解自己的国家和文化，出去之前不会觉得自己的国家文化有什么特别，出去之后会发现自己的文化是如此的丰富和璀璨，会开始很认真的学习自己文化和历史。另外就是一种从不同角度看问题的思维，很多事情都不是非黑即白的</t>
+          <t>The biggest gain from going abroad is understanding your own country and culture. Before going, you might not think your culture is special, but after going, you'll realize how rich and brilliant it is, and you'll start seriously studying your culture and history. Also, you develop the ability to see things from different perspectives; many issues aren't just black or white.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>14小时前</t>
+          <t>14 hours ago</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>18</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>62,山有流云,出国最大的收获就是了解自己的国家和文化，出去之前不会觉得自己的国家文化有什么特别，出去之后会发现自己的文化是如此的丰富和璀璨，会开始很认真的学习自己文化和历史。另外就是一种从不同角度看问题的思维，很多事情都不是非黑即白的,14小时前,澳大利亚,18</t>
-        </is>
       </c>
     </row>
     <row r="64">
@@ -2510,26 +2195,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>能接触到最顶尖的大脑思维和学术态度</t>
+          <t>You get to engage with the top minds and academic attitudes.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>2</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>63,会发光的七七,能接触到最顶尖的大脑思维和学术态度,22小时前,澳大利亚,2</t>
-        </is>
       </c>
     </row>
     <row r="65">
@@ -2543,26 +2223,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>学会对话和提问，怎样跟人家去沟通和辩论，学会找各种资料和验证资料</t>
+          <t>Learn how to have conversations and ask questions, how to communicate and debate with others, and how to find and verify various information.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>2</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>64,Sylvia8383,学会对话和提问，怎样跟人家去沟通和辩论，学会找各种资料和验证资料,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -2576,26 +2251,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>这个经历让我不会再通过一个新闻事件或者社交媒体片段就武断地下结论</t>
+          <t>This experience taught me not to jump to conclusions based on a single news event or a snippet from social media.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>13 hours ago</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>17</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>65,落落与路,这个经历让我不会再通过一个新闻事件或者社交媒体片段就武断地下结论,13小时前,英国,17</t>
-        </is>
       </c>
     </row>
     <row r="67">
@@ -2609,26 +2279,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>体制内文化向体制外文化的转换</t>
+          <t>The shift from an institutional culture to an outside-institution culture.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>66,甜甜🧸,体制内文化向体制外文化的转换,21小时前,澳大利亚,0</t>
-        </is>
       </c>
     </row>
     <row r="68">
@@ -2642,26 +2307,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>从被喂食到学会吃饭，从被动学习到主动学习</t>
+          <t>From being spoon-fed to learning how to feed yourself, from passive learning to active learning.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12小时前</t>
+          <t>12 hours ago</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>4</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>67,爱吃饭的杨小胖,从被喂食到学会吃饭，从被动学习到主动学习,12小时前,德国,4</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -2675,26 +2335,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>学会换位思考，学会理解别人</t>
+          <t>Learn to put yourself in others' shoes and understand them.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>23小时前</t>
+          <t>23 hours ago</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>4</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>68,小星星,学会换位思考，学会理解别人,23小时前,加拿大,4</t>
-        </is>
       </c>
     </row>
     <row r="70">
@@ -2708,26 +2363,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>如何与世界建立联系</t>
+          <t>How to connect with the world.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>1 hours ago</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>3</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>69,美樂塔,如何与世界建立联系,1小时前,英国,3</t>
-        </is>
       </c>
     </row>
     <row r="71">
@@ -2741,26 +2391,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>学会独立思考，critically</t>
+          <t>Learn to think independently, critically.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>70,Heidy,学会独立思考，critically,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="72">
@@ -2774,26 +2419,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>critical thinking批判性思维</t>
+          <t>Critical thinking.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>9</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>71,Momo,critical thinking批判性思维,22小时前,美国,9</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -2807,26 +2447,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>一句话：学会了如何学习</t>
+          <t>In one sentence: learned how to learn.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>4</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>72,咩咩咩咩咩阿,一句话：学会了如何学习,20小时前,美国,4</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -2840,26 +2475,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>critical thinking</t>
+          <t>Critical thinking.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18小时前</t>
+          <t>18 hours ago</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>73,小红薯6F9FFA39,critical thinking,18小时前,澳大利亚,0</t>
-        </is>
       </c>
     </row>
     <row r="75">
@@ -2873,26 +2503,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>虽然不能说唯一，但最核心的价值在于思辨能力和自由表达的能力，知道怎么去表达自己的想法和观点。换个角度看，回国之后我觉得这个比较……稀有</t>
+          <t>Though not the only thing, the core value lies in the ability to think critically and express yourself freely, knowing how to articulate your ideas and opinions. From another angle, after returning to China, I feel this is quite... rare.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7小时前</t>
+          <t>7 hours ago</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>11</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>74,Yuririn,虽然不能说唯一，但最核心的价值在于思辨能力和自由表达的能力，知道怎么去表达自己的想法和观点。换个角度看，回国之后我觉得这个比较……稀有,7小时前,美国,11</t>
-        </is>
       </c>
     </row>
     <row r="76">
@@ -2906,26 +2531,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>对抗权威的自信</t>
+          <t>Confidence to challenge authority.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>2 days ago</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>26</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>75,SenTTTT,对抗权威的自信,2天前,加拿大,26</t>
-        </is>
       </c>
     </row>
     <row r="77">
@@ -2939,26 +2559,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>确实会有点更critical，但也不全是好事hh然后就是，变得更加的inclusive和多元化了</t>
+          <t>It does make you a bit more critical, but that's not always a good thing haha. Also, you become more inclusive and diverse.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10小时前</t>
+          <t>10 hours ago</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>76,Daisy,确实会有点更critical，但也不全是好事hh然后就是，变得更加的inclusive和多元化了,10小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="78">
@@ -2972,26 +2587,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>一切都是垃圾，所有环境都无对错，关键在于你要什么</t>
+          <t>Everything is trash, no environment is right or wrong; it all depends on what you want.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>27</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>77,长颈鹿不抬头,一切都是垃圾，所有环境都无对错，关键在于你要什么,21小时前,德国,27</t>
-        </is>
       </c>
     </row>
     <row r="79">
@@ -3005,26 +2615,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>不是留过学的，来泼个冷水，你想要开拓思维，独立思考，完全可以通过阅读很多经典的社科书籍来实现</t>
+          <t>Not someone who studied abroad, just here to burst your bubble: if you want to broaden your thinking and think independently, you can totally do that by reading lots of classic social science books.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>14</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>78,小艾哥在路上,不是留过学的，来泼个冷水，你想要开拓思维，独立思考，完全可以通过阅读很多经典的社科书籍来实现,1天前,北京,14</t>
-        </is>
       </c>
     </row>
     <row r="80">
@@ -3038,26 +2643,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>留学的价值不在于学校名气，而在于体验另一种生活方式，接触不同的人，看到更广阔的世界</t>
+          <t>The value of studying abroad isn't in the school's reputation, but in experiencing a different lifestyle, meeting different people, and seeing a broader world.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>79,小红薯678D4CA3,留学的价值不在于学校名气，而在于体验另一种生活方式，接触不同的人，看到更广阔的世界,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="81">
@@ -3071,26 +2671,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>能感受到很多思想上的冲击，看到和接触到不同的政治制度，不同的社会形态</t>
+          <t>You can feel a lot of ideological shocks, see and experience different political systems and social forms.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>18小时前</t>
+          <t>18 hours ago</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>8</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>80,莎莎酱,能感受到很多思想上的冲击，看到和接触到不同的政治制度，不同的社会形态,18小时前,英国,8</t>
-        </is>
       </c>
     </row>
     <row r="82">
@@ -3104,26 +2699,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>完成学历提升，同时在一个自由的思想环境下学会独立思考</t>
+          <t>Completed academic advancement while learning to think independently in a free-thinking environment.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23小时前</t>
+          <t>23 hours ago</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>81,陈一朵,完成学历提升，同时在一个自由的思想环境下学会独立思考,23小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="83">
@@ -3137,26 +2727,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>critical thinking独立思辨性思维，not taking things for granted不把一切视为理所当然</t>
+          <t>Critical thinking—independent and reflective thinking, not taking things for granted.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>7小时前</t>
+          <t>7 hours ago</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>12</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>82,尐莮,critical thinking独立思辨性思维，not taking things for granted不把一切视为理所当然,7小时前,英国,12</t>
-        </is>
       </c>
     </row>
     <row r="84">
@@ -3170,26 +2755,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>critical thinking批判性思维</t>
+          <t>Critical thinking.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>18小时前</t>
+          <t>18 hours ago</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>83,洋葱圈,critical thinking批判性思维,18小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="85">
@@ -3203,26 +2783,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>学会独立思考，形成自己的价值观</t>
+          <t>Learned to think independently and form my own values.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>84,小熊饼干盒子,学会独立思考，形成自己的价值观,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="86">
@@ -3236,26 +2811,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>发现自己爱国了</t>
+          <t>Discovered that I love my country.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2天前</t>
+          <t>2 days ago</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>78</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>85,Zoey,发现自己爱国了,2天前,美国,78</t>
-        </is>
       </c>
     </row>
     <row r="87">
@@ -3269,26 +2839,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>对于探索未知的勇气，不会再害怕改变</t>
+          <t>Gained the courage to explore the unknown and no longer fear change.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>86,啦啦啦拉拉,对于探索未知的勇气，不会再害怕改变,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="88">
@@ -3302,26 +2867,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>学会了批判性思维，看待问题更全面了</t>
+          <t>Learned critical thinking and now see issues more comprehensively.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>87,小红薯69E8B8C4,学会了批判性思维，看待问题更全面了,22小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="89">
@@ -3335,26 +2895,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>独立思考能力，critical thinking</t>
+          <t>Independent thinking ability, critical thinking.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>2</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>88,Rena,独立思考能力，critical thinking,1天前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="90">
@@ -3368,26 +2923,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>看到了不同制度、不同文化下的人们是如何生活的，understand diversity</t>
+          <t>Saw how people live under different systems and cultures, understand diversity.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>13 hours ago</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>2</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>89,林深时见鹿_,看到了不同制度、不同文化下的人们是如何生活的，understand diversity,13小时前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="91">
@@ -3401,26 +2951,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>学会了接受不完美，学会了be comfortable with being uncomfortable</t>
+          <t>Learned to accept imperfection and be comfortable with being uncomfortable.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>4</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>90,阿西吧不是阿西八,学会了接受不完美，学会了be comfortable with being uncomfortable,22小时前,美国,4</t>
-        </is>
       </c>
     </row>
     <row r="92">
@@ -3434,26 +2979,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>独立思考critical thinking，多元价值观，尊重差异</t>
+          <t>Independent thinking, critical thinking, diverse values, respect differences.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>18小时前</t>
+          <t>18 hours ago</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>91,YY,独立思考critical thinking，多元价值观，尊重差异,18小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="93">
@@ -3467,26 +3007,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>critical thinking批判性思维，这是最重要的</t>
+          <t>Critical thinking—this is the most important.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>3</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>92,SSSS,critical thinking批判性思维，这是最重要的,1天前,加拿大,3</t>
-        </is>
       </c>
     </row>
     <row r="94">
@@ -3500,26 +3035,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>critical thinking，学会质疑和独立思考</t>
+          <t>Critical thinking, learned to question and think independently.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>93,小小,critical thinking，学会质疑和独立思考,19小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="95">
@@ -3533,26 +3063,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>建立了批判性思维模式</t>
+          <t>Established a critical thinking mindset.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>1</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>94,Echo回声,建立了批判性思维模式,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="96">
@@ -3566,26 +3091,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>critical thinking批判性思维！这是我觉得最重要的</t>
+          <t>Critical thinking! This is what I think is most important.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>2</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>95,虹虹,critical thinking批判性思维！这是我觉得最重要的,21小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="97">
@@ -3599,26 +3119,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>学会了独立生活，建立自己的社交圈，独立思考</t>
+          <t>Learned to live independently, build my own social circle, and think independently.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>96,啊哈哈哈,学会了独立生活，建立自己的社交圈，独立思考,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="98">
@@ -3632,26 +3147,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>批判性思维critical thinking</t>
+          <t>Critical thinking.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>1</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>97,Nicole,批判性思维critical thinking,22小时前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="99">
@@ -3665,26 +3175,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>critical thinking批判性思维，学会去质疑而不是全盘接受</t>
+          <t>Critical thinking, learned to question instead of blindly accepting.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>18小时前</t>
+          <t>18 hours ago</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>2</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>98,沐沐,critical thinking批判性思维，学会去质疑而不是全盘接受,18小时前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="100">
@@ -3698,26 +3203,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>比起知识本身，我学会了如何学习，如何独立思考</t>
+          <t>More than knowledge itself, I learned how to learn and how to think independently.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>1</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>99,小糖,比起知识本身，我学会了如何学习，如何独立思考,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="101">
@@ -3731,44 +3231,30 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>建立了真正的critical thinking</t>
+          <t>Established true critical thinking.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>3</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>100,Lily,建立了真正的critical thinking,19小时前,英国,3</t>
-        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3781,26 +3267,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>批判性思维模式的养成</t>
+          <t>The development of critical thinking patterns</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>1</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>101,小小酥,批判性思维模式的养成,21小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="104">
@@ -3814,26 +3295,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>学会了如何与人沟通，如何解决问题</t>
+          <t>Learned how to communicate with others and solve problems</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>0</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>102,momo,学会了如何与人沟通，如何解决问题,1天前,美国,0</t>
-        </is>
       </c>
     </row>
     <row r="105">
@@ -3847,26 +3323,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>开拓眼界，尊重多元文化</t>
+          <t>Broadened horizons, respect for multiculturalism</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>1</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>103,咕噜咕噜,开拓眼界，尊重多元文化,19小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="106">
@@ -3880,26 +3351,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>独立思考的能力，不再盲从</t>
+          <t>The ability to think independently, no longer blindly follow</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>2</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>104,小红薯6B4E5F6A,独立思考的能力，不再盲从,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="107">
@@ -3913,26 +3379,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>critical thinking和表达能力</t>
+          <t>Critical thinking and expression skills</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>1</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>105,泡泡,critical thinking和表达能力,20小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="108">
@@ -3946,26 +3407,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>学会了接受不同，建立了自己的价值观</t>
+          <t>Learned to accept differences and established my own values</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>1</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>106,阿珍,学会了接受不同，建立了自己的价值观,22小时前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="109">
@@ -3979,26 +3435,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>思辨能力的提升，独立的人格</t>
+          <t>Improved reasoning ability, independent personality</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F109" t="n">
         <v>1</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>107,大王叫我来巡山,思辨能力的提升，独立的人格,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="110">
@@ -4012,26 +3463,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>开拓眼界，学会包容</t>
+          <t>Broadened horizons, learned to be tolerant</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>18小时前</t>
+          <t>18 hours ago</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>0</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>108,小方,开拓眼界，学会包容,18小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="111">
@@ -4045,26 +3491,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>批判性思维critical thinking</t>
+          <t>Critical thinking</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>2</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>109,皮皮,批判性思维critical thinking,21小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="112">
@@ -4078,26 +3519,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>独立思考，不被舆论左右</t>
+          <t>Independent thinking, not swayed by public opinion</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>1</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>110,安安,独立思考，不被舆论左右,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="113">
@@ -4111,26 +3547,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>学会了如何去学习，如何去思考</t>
+          <t>Learned how to learn and how to think</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>1</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>111,momo,学会了如何去学习，如何去思考,19小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="114">
@@ -4144,26 +3575,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>建立了自己的评价体系，不再活在别人的眼光里</t>
+          <t>Established my own evaluation system, no longer living under others' gaze</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>4</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>112,小红薯6C5D4E3F,建立了自己的评价体系，不再活在别人的眼光里,22小时前,美国,4</t>
-        </is>
       </c>
     </row>
     <row r="115">
@@ -4177,26 +3603,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>critical thinking，这是留学的灵魂</t>
+          <t>Critical thinking, the soul of studying abroad</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F115" t="n">
         <v>2</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>113,七七,critical thinking，这是留学的灵魂,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="116">
@@ -4210,26 +3631,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>学会了独立生活，独立思考</t>
+          <t>Learned to live independently and think independently</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>114,肉肉,学会了独立生活，独立思考,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="117">
@@ -4243,26 +3659,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>开拓了眼界，见识了不一样的世界</t>
+          <t>Broadened horizons, experienced a different world</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F117" t="n">
         <v>1</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>115,小太阳,开拓了眼界，见识了不一样的世界,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="118">
@@ -4276,26 +3687,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>批判性思维能力的建立</t>
+          <t>The establishment of critical thinking ability</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F118" t="n">
         <v>1</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>116,草莓酱,批判性思维能力的建立,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="119">
@@ -4309,26 +3715,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>学会了尊重差异，理解多元文化</t>
+          <t>Learned to respect differences and understand multiculturalism</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>1</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>117,阿强,学会了尊重差异，理解多元文化,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="120">
@@ -4342,26 +3743,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>独立思考，独立生活</t>
+          <t>Independent thinking, independent living</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F120" t="n">
         <v>0</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>118,小红薯6A9B8C7D,独立思考，独立生活,22小时前,美国,0</t>
-        </is>
       </c>
     </row>
     <row r="121">
@@ -4375,26 +3771,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>critical thinking和多元价值观</t>
+          <t>Critical thinking and diverse values</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>2</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>119,西西,critical thinking和多元价值观,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="122">
@@ -4408,26 +3799,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>建立了批判性思维，学会了质疑</t>
+          <t>Developed critical thinking and learned to question</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F122" t="n">
         <v>1</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>120,多多,建立了批判性思维，学会了质疑,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="123">
@@ -4441,26 +3827,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>开拓眼界，提升认知</t>
+          <t>Broadened horizons and enhanced understanding</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F123" t="n">
         <v>1</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>121,小宇,开拓眼界，提升认知,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="124">
@@ -4474,26 +3855,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>批判性思维模式的养成</t>
+          <t>Cultivated a critical thinking mindset</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>1</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>122,琳琳,批判性思维模式的养成,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="125">
@@ -4507,26 +3883,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>学会了如何独立面对困难，独立思考</t>
+          <t>Learned how to face difficulties independently and think for myself</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F125" t="n">
         <v>1</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>123,momo,学会了如何独立面对困难，独立思考,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="126">
@@ -4540,26 +3911,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>建立了自己的思想体系</t>
+          <t>Built my own system of thought</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>2</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>124,小红薯6D5E4F3A,建立了自己的思想体系,22小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="127">
@@ -4573,26 +3939,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>critical thinking，最宝贵的财富</t>
+          <t>Critical thinking, the most valuable treasure</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F127" t="n">
         <v>1</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>125,贝贝,critical thinking，最宝贵的财富,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="128">
@@ -4606,26 +3967,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>开拓眼界，丰富阅历</t>
+          <t>Broadened horizons and enriched experiences</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F128" t="n">
         <v>0</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>126,欢欢,开拓眼界，丰富阅历,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="129">
@@ -4639,26 +3995,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>学会了独立思考，不盲从权威</t>
+          <t>Learned to think independently and not blindly follow authority</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F129" t="n">
         <v>1</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>127,小明,学会了独立思考，不盲从权威,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="130">
@@ -4672,26 +4023,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>批判性思维能力的提升</t>
+          <t>Improved critical thinking skills</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F130" t="n">
         <v>1</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>128,圆圆,批判性思维能力的提升,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="131">
@@ -4705,26 +4051,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>学会了包容不同文化，尊重差异</t>
+          <t>Learned to embrace different cultures and respect differences</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F131" t="n">
         <v>1</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>129,阿花,学会了包容不同文化，尊重差异,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="132">
@@ -4738,26 +4079,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>建立了自己的独立人格</t>
+          <t>Established my own independent personality</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F132" t="n">
         <v>3</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>130,小红薯6E5D4C3B,建立了自己的独立人格,22小时前,美国,3</t>
-        </is>
       </c>
     </row>
     <row r="133">
@@ -4771,26 +4107,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>critical thinking和思辨能力</t>
+          <t>Critical thinking and reasoning skills</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F133" t="n">
         <v>1</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>131,甜甜,critical thinking和思辨能力,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="134">
@@ -4804,26 +4135,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>开拓眼界，增长见识</t>
+          <t>Broadened horizons and gained knowledge</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F134" t="n">
         <v>0</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>132,果果,开拓眼界，增长见识,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="135">
@@ -4837,26 +4163,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>学会了如何独立思考，如何生活</t>
+          <t>Learned how to think independently and how to live</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F135" t="n">
         <v>1</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>133,小刚,学会了如何独立思考，如何生活,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="136">
@@ -4870,26 +4191,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>批判性思维模式的建立</t>
+          <t>Established a critical thinking pattern</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F136" t="n">
         <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>134,萌萌,批判性思维模式的建立,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="137">
@@ -4903,26 +4219,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>学会了尊重多元文化，理解包容</t>
+          <t>Learned to respect multiculturalism and practice understanding and tolerance</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F137" t="n">
         <v>1</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>135,阿力,学会了尊重多元文化，理解包容,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="138">
@@ -4936,26 +4247,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>独立思考，不再被洗脑</t>
+          <t>Think independently, no longer brainwashed</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F138" t="n">
         <v>5</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>136,小红薯6F5E4D3C,独立思考，不再被洗脑,22小时前,美国,5</t>
-        </is>
       </c>
     </row>
     <row r="139">
@@ -4969,26 +4275,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>critical thinking和独立人格</t>
+          <t>Critical thinking and independent personality</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>2</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>137,佳佳,critical thinking和独立人格,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="140">
@@ -5002,26 +4303,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>开拓眼界，提升思维深度</t>
+          <t>Broadened horizons and deepened thinking</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F140" t="n">
         <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>138,晨晨,开拓眼界，提升思维深度,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="141">
@@ -5035,26 +4331,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>学会了批判性地看待问题</t>
+          <t>Learned to look at problems critically</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F141" t="n">
         <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>139,小王,学会了批判性地看待问题,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="142">
@@ -5068,26 +4359,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>批判性思维能力的养成</t>
+          <t>The development of critical thinking skills</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F142" t="n">
         <v>1</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>140,曼曼,批判性思维能力的养成,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="143">
@@ -5101,26 +4387,21 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>学会了独立生活，独立思考</t>
+          <t>Learned to live independently and think independently</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F143" t="n">
         <v>1</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>141,阿水,学会了独立生活，独立思考,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="144">
@@ -5134,26 +4415,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>建立了自己的价值观体系</t>
+          <t>Established my own value system</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F144" t="n">
         <v>2</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>142,小红薯6G5F4E3D,建立了自己的价值观体系,22小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="145">
@@ -5167,26 +4443,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>critical thinking，留学的核心价值</t>
+          <t>Critical thinking, the core value of studying abroad</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F145" t="n">
         <v>1</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>143,玲玲,critical thinking，留学的核心价值,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="146">
@@ -5200,26 +4471,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>开拓眼界，丰富人生体验</t>
+          <t>Broadened horizons, enriched life experiences</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F146" t="n">
         <v>0</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>144,明明,开拓眼界，丰富人生体验,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="147">
@@ -5233,26 +4499,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>学会了独立思考，提升了认知</t>
+          <t>Learned to think independently, improved cognition</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F147" t="n">
         <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>145,小李,学会了独立思考，提升了认知,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="148">
@@ -5266,26 +4527,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>批判性思维模式的提升</t>
+          <t>Improvement of critical thinking patterns</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F148" t="n">
         <v>1</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>146,青青,批判性思维模式的提升,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="149">
@@ -5299,26 +4555,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>学会了包容差异，尊重多元</t>
+          <t>Learned to embrace differences and respect diversity</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F149" t="n">
         <v>1</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>147,阿木,学会了包容差异，尊重多元,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="150">
@@ -5332,26 +4583,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>建立了独立的人格和思想</t>
+          <t>Established an independent personality and mindset</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F150" t="n">
         <v>4</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>148,小红薯6H5G4F3E,建立了独立的人格和思想,22小时前,美国,4</t>
-        </is>
       </c>
     </row>
     <row r="151">
@@ -5365,26 +4611,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>critical thinking和思辨能力</t>
+          <t>Critical thinking and reasoning skills</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F151" t="n">
         <v>1</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>149,芳芳,critical thinking和思辨能力,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="152">
@@ -5398,26 +4639,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>开拓眼界，提升格局</t>
+          <t>Broadened horizons, elevated perspective</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>1</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>150,建建,开拓眼界，提升格局,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="153">
@@ -5431,26 +4667,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>批判性思维模式的建立</t>
+          <t>Establishment of critical thinking patterns</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F153" t="n">
         <v>1</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>151,小美,批判性思维模式的建立,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="154">
@@ -5464,26 +4695,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>学会了尊重多元文化，理解包容</t>
+          <t>Learned to respect multiculturalism, understand and embrace it</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F154" t="n">
         <v>1</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>152,阿华,学会了尊重多元文化，理解包容,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="155">
@@ -5497,26 +4723,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>独立思考，不再被带节奏</t>
+          <t>Think independently, no longer follow the crowd blindly</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F155" t="n">
         <v>5</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>153,小红薯6I5H4G3F,独立思考，不再被带节奏,22小时前,美国,5</t>
-        </is>
       </c>
     </row>
     <row r="156">
@@ -5530,26 +4751,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>critical thinking和独立精神</t>
+          <t>Critical thinking and independent spirit</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>2</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>154,琳琳,critical thinking和独立精神,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="157">
@@ -5563,26 +4779,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>开拓眼界，提升思维认知</t>
+          <t>Broadened horizons, enhanced cognitive thinking</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F157" t="n">
         <v>1</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>155,多多,开拓眼界，提升思维认知,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="158">
@@ -5596,26 +4807,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>学会了从不同角度看世界</t>
+          <t>Learned to see the world from different angles</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F158" t="n">
         <v>1</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>156,小王,学会了从不同角度看世界,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="159">
@@ -5629,26 +4835,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>批判性思维能力的建立</t>
+          <t>The establishment of critical thinking ability</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F159" t="n">
         <v>1</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>157,曼曼,批判性思维能力的建立,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="160">
@@ -5662,26 +4863,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>学会了独立面对一切</t>
+          <t>Learned to face everything independently</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F160" t="n">
         <v>1</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>158,阿水,学会了独立面对一切,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="161">
@@ -5695,26 +4891,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>建立了稳固的自我意识</t>
+          <t>Established a solid self-awareness</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F161" t="n">
         <v>2</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>159,小红薯6J5I4H3G,建立了稳固的自我意识,22小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="162">
@@ -5728,26 +4919,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>critical thinking，终身受用</t>
+          <t>Critical thinking, a lifelong benefit</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F162" t="n">
         <v>1</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>160,玲玲,critical thinking，终身受用,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="163">
@@ -5761,26 +4947,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>开拓眼界，增长见闻</t>
+          <t>Broaden horizons, increase knowledge</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F163" t="n">
         <v>0</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>161,明明,开拓眼界，增长见闻,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="164">
@@ -5794,26 +4975,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>学会了独立思考和判断</t>
+          <t>Learned to think and judge independently</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F164" t="n">
         <v>1</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>162,小李,学会了独立思考和判断,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="165">
@@ -5827,26 +5003,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>批判性思维模式的养成</t>
+          <t>Development of a critical thinking mindset</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F165" t="n">
         <v>1</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>163,青青,批判性思维模式的养成,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="166">
@@ -5860,26 +5031,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>学会了尊重差异，理解包容</t>
+          <t>Learned to respect differences, understand and tolerate</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F166" t="n">
         <v>1</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>164,阿木,学会了尊重差异，理解包容,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="167">
@@ -5893,26 +5059,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>建立了独立的人格底气</t>
+          <t>Built an independent and confident personality</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>4</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>165,小红薯6K5J4I3H,建立了独立的人格底气,22小时前,美国,4</t>
-        </is>
       </c>
     </row>
     <row r="168">
@@ -5926,26 +5087,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>critical thinking和表达能力</t>
+          <t>Critical thinking and expression skills</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F168" t="n">
         <v>1</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>166,芳芳,critical thinking和表达能力,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="169">
@@ -5959,26 +5115,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>开拓眼界，提升自我认知</t>
+          <t>Broaden horizons, enhance self-awareness</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F169" t="n">
         <v>1</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>167,建建,开拓眼界，提升自我认知,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="170">
@@ -5992,26 +5143,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>学会了独立思考和生活</t>
+          <t>Learned to think and live independently</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F170" t="n">
         <v>1</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>168,小红,学会了独立思考和生活,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="171">
@@ -6025,26 +5171,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>批判性思维能力的养成</t>
+          <t>Cultivation of critical thinking skills</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F171" t="n">
         <v>1</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>169,莉莉,批判性思维能力的养成,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="172">
@@ -6058,26 +5199,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>学会了包容不同，尊重多元</t>
+          <t>Learned to embrace diversity and respect pluralism</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F172" t="n">
         <v>1</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>170,大伟,学会了包容不同，尊重多元,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="173">
@@ -6091,26 +5227,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>建立了清晰的价值观体系</t>
+          <t>Established a clear value system</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F173" t="n">
         <v>3</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>171,小红薯6L5K4J3I,建立了清晰的价值观体系,22小时前,美国,3</t>
-        </is>
       </c>
     </row>
     <row r="174">
@@ -6124,26 +5255,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>critical thinking和逻辑思维</t>
+          <t>Critical thinking and logical reasoning</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F174" t="n">
         <v>1</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>172,兰兰,critical thinking和逻辑思维,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="175">
@@ -6157,26 +5283,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>开拓眼界，丰富人生体验</t>
+          <t>Broaden horizons, enrich life experiences</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F175" t="n">
         <v>0</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>173,亮亮,开拓眼界，丰富人生体验,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="176">
@@ -6190,26 +5311,21 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>学会了独立思考和判断是非</t>
+          <t>Learned to think independently and judge right from wrong</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F176" t="n">
         <v>1</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>174,小明,学会了独立思考和判断是非,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="177">
@@ -6223,26 +5339,21 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>批判性思维模式的建立</t>
+          <t>Formation of a critical thinking pattern</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F177" t="n">
         <v>1</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>175,红红,批判性思维模式的建立,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="178">
@@ -6256,26 +5367,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>学会了尊重多元，理解差异</t>
+          <t>Learned to respect diversity and understand differences</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F178" t="n">
         <v>1</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>176,阿强,学会了尊重多元，理解差异,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="179">
@@ -6289,26 +5395,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>建立了独立思考的习惯</t>
+          <t>Established the habit of independent thinking</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F179" t="n">
         <v>2</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>177,小红薯6M5L4K3J,建立了独立思考的习惯,22小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="180">
@@ -6322,26 +5423,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>critical thinking和独立自主</t>
+          <t>Critical thinking and independence</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F180" t="n">
         <v>2</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>178,娟娟,critical thinking和独立自主,1天前,英国,2</t>
-        </is>
       </c>
     </row>
     <row r="181">
@@ -6355,26 +5451,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>开拓眼界，提升格局观</t>
+          <t>Broaden horizons, elevate perspective</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F181" t="n">
         <v>1</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>179,楠楠,开拓眼界，提升格局观,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="182">
@@ -6388,26 +5479,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>学会了批判性看待问题</t>
+          <t>Learned to view problems critically</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F182" t="n">
         <v>1</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>180,小赵,学会了批判性看待问题,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="183">
@@ -6421,26 +5507,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>批判性思维能力的养成</t>
+          <t>Development of critical thinking skills</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F183" t="n">
         <v>1</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>181,梅梅,批判性思维能力的养成,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="184">
@@ -6454,26 +5535,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>学会了独立面对挑战</t>
+          <t>Learned to face challenges independently</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F184" t="n">
         <v>1</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>182,阿健,学会了独立面对挑战,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="185">
@@ -6487,26 +5563,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>建立了独特的观察视角</t>
+          <t>Established a unique perspective of observation</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F185" t="n">
         <v>2</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>183,小红薯6N5M4L3K,建立了独特的观察视角,22小时前,美国,2</t>
-        </is>
       </c>
     </row>
     <row r="186">
@@ -6520,26 +5591,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>critical thinking和多元认知</t>
+          <t>Critical thinking and diverse cognition</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F186" t="n">
         <v>1</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>184,婷婷,critical thinking和多元认知,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="187">
@@ -6553,26 +5619,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>开拓眼界，丰富精神世界</t>
+          <t>Broadened horizons, enriched the spiritual world</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F187" t="n">
         <v>0</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>185,峰峰,开拓眼界，丰富精神世界,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="188">
@@ -6586,26 +5647,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>学会了独立思考和抉择</t>
+          <t>Learned to think and make choices independently</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F188" t="n">
         <v>1</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>186,小钱,学会了独立思考和抉择,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="189">
@@ -6619,26 +5675,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>批判性思维模式的提升</t>
+          <t>Improvement of critical thinking patterns</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F189" t="n">
         <v>1</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>187,慧慧,批判性思维模式的提升,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="190">
@@ -6652,26 +5703,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>学会了尊重不同，包容差异</t>
+          <t>Learned to respect differences and embrace diversity</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F190" t="n">
         <v>1</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>188,阿德,学会了尊重不同，包容差异,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="191">
@@ -6685,26 +5731,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>建立了稳固的内心世界</t>
+          <t>Built a solid inner world</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F191" t="n">
         <v>4</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>189,小红薯6O5P4Q3R,建立了稳固的内心世界,22小时前,美国,4</t>
-        </is>
       </c>
     </row>
     <row r="192">
@@ -6718,26 +5759,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>critical thinking和独立见解</t>
+          <t>Critical thinking and independent insights</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F192" t="n">
         <v>1</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>190,艳艳,critical thinking和独立见解,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="193">
@@ -6751,26 +5787,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>开拓眼界，提升综合素质</t>
+          <t>Broadened horizons, enhanced overall quality</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F193" t="n">
         <v>1</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>191,刚刚,开拓眼界，提升综合素质,20小时前,加拿大,1</t>
-        </is>
       </c>
     </row>
     <row r="194">
@@ -6784,26 +5815,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>学会了独立思考和成长</t>
+          <t>Learned to think independently and grow</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F194" t="n">
         <v>1</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>192,小孙,学会了独立思考和成长,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="195">
@@ -6817,26 +5843,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>批判性思维能力的养成</t>
+          <t>Development of critical thinking skills</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F195" t="n">
         <v>1</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>193,平平,批判性思维能力的养成,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="196">
@@ -6850,26 +5871,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>学会了包容差异，理解多元</t>
+          <t>Learned to embrace differences and understand diversity</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F196" t="n">
         <v>1</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>194,阿诚,学会了包容差异，理解多元,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
     <row r="197">
@@ -6883,26 +5899,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>建立了独立思考的底座</t>
+          <t>Built a foundation for independent thinking</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>22小时前</t>
+          <t>22 hours ago</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F197" t="n">
         <v>3</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>195,小红薯6S5T4U3V,建立了独立思考的底座,22小时前,美国,3</t>
-        </is>
       </c>
     </row>
     <row r="198">
@@ -6916,26 +5927,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>critical thinking和逻辑能力</t>
+          <t>Critical thinking and logical skills</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F198" t="n">
         <v>1</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>196,丹丹,critical thinking和逻辑能力,1天前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="199">
@@ -6949,26 +5955,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>开拓眼界，增强自信心</t>
+          <t>Broadened horizons, boosted confidence</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20小时前</t>
+          <t>20 hours ago</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F199" t="n">
         <v>0</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>197,志志,开拓眼界，增强自信心,20小时前,加拿大,0</t>
-        </is>
       </c>
     </row>
     <row r="200">
@@ -6982,26 +5983,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>学会了独立思考和解决问题</t>
+          <t>Learned to think independently and solve problems</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1天前</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F200" t="n">
         <v>1</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>198,小周,学会了独立思考和解决问题,1天前,美国,1</t>
-        </is>
       </c>
     </row>
     <row r="201">
@@ -7015,26 +6011,21 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>批判性思维模式的建立</t>
+          <t>Established critical thinking patterns</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>19小时前</t>
+          <t>19 hours ago</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F201" t="n">
         <v>1</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>199,丽丽,批判性思维模式的建立,19小时前,英国,1</t>
-        </is>
       </c>
     </row>
     <row r="202">
@@ -7048,26 +6039,21 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>学会了尊重差异，拥抱多样性</t>
+          <t>Learned to respect differences and embrace diversity</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>21小时前</t>
+          <t>21 hours ago</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F202" t="n">
         <v>1</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>200,阿山,学会了尊重差异，拥抱多样性,21小时前,澳大利亚,1</t>
-        </is>
       </c>
     </row>
   </sheetData>
